--- a/tests/coil_3D_avoltemf_edge_ferr/input_template.xlsx
+++ b/tests/coil_3D_avoltemf_edge_ferr/input_template.xlsx
@@ -177,7 +177,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +188,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -239,10 +245,10 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -602,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -625,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -648,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -671,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
